--- a/Figure 2/Figure 2-E.xlsx
+++ b/Figure 2/Figure 2-E.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34BBF41B-4635-4C52-85A9-2E1043CC14AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C48651A1-5E48-4247-9E48-FB19B2D575C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26170" yWindow="2700" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +167,12 @@
       <name val="等线"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -188,13 +194,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -481,353 +488,354 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8.6640625" style="3"/>
+    <col min="2" max="4" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>283.04660086666667</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="4">
         <v>442.55132800000007</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="4">
         <v>0.63957914699999996</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>262.74771189999973</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="4">
         <v>547.65788099999941</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="4">
         <v>0.479766148</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>355.1073126666663</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="4">
         <v>345.49962933333296</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
         <v>1.0278080860000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>334.40574733333301</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="4">
         <v>425.00135566666626</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="4">
         <v>0.786834543</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>250.57179629999973</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="4">
         <v>472.89255566666623</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="4">
         <v>0.52987046100000001</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>296.64370953333304</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="4">
         <v>539.92952366666611</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="4">
         <v>0.54941190699999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>228.98473726666643</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>471.79670199999958</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="4">
         <v>0.485346202</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>223.59038333333314</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="4">
         <v>285.37185613333304</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="4">
         <v>0.78350537600000003</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>268.19730666666641</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="4">
         <v>416.77145666666621</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="4">
         <v>0.64351169500000005</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>273.36505926666638</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="4">
         <v>422.53513333333291</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="4">
         <v>0.64696409300000002</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>241.48746943333308</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="4">
         <v>368.8613906666663</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="4">
         <v>0.65468350900000005</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>287.23210443333306</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="4">
         <v>348.64828066666632</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="4">
         <v>0.82384489000000005</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>291.74361866666635</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="4">
         <v>478.12272666666615</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="4">
         <v>0.61018563299999995</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>236.49263143333309</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="4">
         <v>417.93229799999961</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="4">
         <v>0.56586349599999997</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>322.35685883333298</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="4">
         <v>500.45366366666616</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="4">
         <v>0.64412928199999997</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>317.78655799999967</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="4">
         <v>398.49320599999959</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="4">
         <v>0.79747045400000005</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>226.79128999999975</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="4">
         <v>442.50351666666626</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="4">
         <v>0.51251861600000004</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>295.14165286666639</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="4">
         <v>483.17966433333282</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="4">
         <v>0.61083210799999998</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>255.79234999999974</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="4">
         <v>513.08034033333286</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="4">
         <v>0.49854248899999998</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>208.6173607999998</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="4">
         <v>481.59319199999948</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="4">
         <v>0.433181706</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>239.05094829999976</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="4">
         <v>331.47046906666634</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="4">
         <v>0.721183244</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>222.71738386666641</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="4">
         <v>449.36986333333289</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="4">
         <v>0.49562154000000003</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>310.36415276666639</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="4">
         <v>423.09356766666622</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="4">
         <v>0.73355913800000005</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="4">
         <v>236.55262306666643</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="4">
         <v>386.94322933333297</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="4">
         <v>0.61133676699999995</v>
       </c>
     </row>
